--- a/backend/data/financials_by_company/0658.HK.xlsx
+++ b/backend/data/financials_by_company/0658.HK.xlsx
@@ -667,58 +667,58 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-1711928250</v>
+        <v>-3180696.038547</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.14391</v>
       </c>
       <c r="D2" t="n">
-        <v>2589296000</v>
+        <v>2313699000</v>
       </c>
       <c r="E2" t="n">
-        <v>-6847441000</v>
+        <v>-22102000</v>
       </c>
       <c r="F2" t="n">
-        <v>-6847713000</v>
+        <v>-22102000</v>
       </c>
       <c r="G2" t="n">
-        <v>-6556733000</v>
+        <v>1315245000</v>
       </c>
       <c r="H2" t="n">
-        <v>768838000</v>
+        <v>426425000</v>
       </c>
       <c r="I2" t="n">
-        <v>18787323000</v>
+        <v>17022216000</v>
       </c>
       <c r="J2" t="n">
-        <v>-4258145000</v>
+        <v>2291597000</v>
       </c>
       <c r="K2" t="n">
-        <v>-5026983000</v>
+        <v>1865172000</v>
       </c>
       <c r="L2" t="n">
-        <v>-610766000</v>
+        <v>-37921000</v>
       </c>
       <c r="M2" t="n">
-        <v>726262000</v>
+        <v>233498000</v>
       </c>
       <c r="N2" t="n">
-        <v>115496000</v>
+        <v>195577000</v>
       </c>
       <c r="O2" t="n">
-        <v>-1420676250</v>
+        <v>1334166303.961453</v>
       </c>
       <c r="P2" t="n">
-        <v>-6556733000</v>
+        <v>1315245000</v>
       </c>
       <c r="Q2" t="n">
-        <v>20430185000</v>
+        <v>18467007000</v>
       </c>
       <c r="R2" t="n">
-        <v>-5141118000</v>
+        <v>1826666000</v>
       </c>
       <c r="S2" t="n">
         <v>1635291000</v>
@@ -726,146 +726,148 @@
       <c r="T2" t="n">
         <v>1635291000</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>0.804</v>
+      </c>
       <c r="V2" t="n">
-        <v>-4.01</v>
+        <v>0.804</v>
       </c>
       <c r="W2" t="n">
-        <v>-6556733000</v>
+        <v>1315245000</v>
       </c>
       <c r="X2" t="n">
-        <v>-6556733000</v>
+        <v>1315245000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-6556733000</v>
+        <v>1315245000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-625205000</v>
+        <v>-81615000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-5931528000</v>
+        <v>1396860000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-5931528000</v>
+        <v>1396860000</v>
       </c>
       <c r="AD2" t="n">
-        <v>178283000</v>
+        <v>234814000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-5753245000</v>
+        <v>1631674000</v>
       </c>
       <c r="AF2" t="n">
-        <v>29359000</v>
+        <v>21331000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-6855449000</v>
+        <v>-50786000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-9661000</v>
+        <v>11377000</v>
       </c>
       <c r="AI2" t="n">
-        <v>6870948000</v>
+        <v>-42823000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-6110000</v>
+        <v>82232000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-610766000</v>
+        <v>-37921000</v>
       </c>
       <c r="AL2" t="n">
-        <v>726262000</v>
+        <v>233498000</v>
       </c>
       <c r="AM2" t="n">
-        <v>115496000</v>
+        <v>195577000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1645285000</v>
+        <v>1743519000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1642862000</v>
+        <v>1444791000</v>
       </c>
       <c r="AP2" t="n">
-        <v>809474000</v>
+        <v>667782000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1126315000</v>
+        <v>910303000</v>
       </c>
       <c r="AR2" t="n">
-        <v>541984000</v>
+        <v>430244000</v>
       </c>
       <c r="AS2" t="n">
-        <v>584331000</v>
+        <v>480059000</v>
       </c>
       <c r="AT2" t="n">
-        <v>3288147000</v>
+        <v>3188310000</v>
       </c>
       <c r="AU2" t="n">
-        <v>18787323000</v>
+        <v>17022216000</v>
       </c>
       <c r="AV2" t="n">
-        <v>22075470000</v>
+        <v>20210526000</v>
       </c>
       <c r="AW2" t="n">
-        <v>22075470000</v>
+        <v>20210526000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-48748567.780528</v>
+        <v>-78306358.668634</v>
       </c>
       <c r="C3" t="n">
-        <v>0.154558</v>
+        <v>0.382697</v>
       </c>
       <c r="D3" t="n">
-        <v>2354263000</v>
+        <v>2261704000</v>
       </c>
       <c r="E3" t="n">
-        <v>-315407000</v>
+        <v>-204617000</v>
       </c>
       <c r="F3" t="n">
-        <v>-315407000</v>
+        <v>-204617000</v>
       </c>
       <c r="G3" t="n">
-        <v>95517000</v>
+        <v>101599000</v>
       </c>
       <c r="H3" t="n">
-        <v>547588000</v>
+        <v>424683000</v>
       </c>
       <c r="I3" t="n">
-        <v>20682363000</v>
+        <v>17816422000</v>
       </c>
       <c r="J3" t="n">
-        <v>2038856000</v>
+        <v>2057087000</v>
       </c>
       <c r="K3" t="n">
-        <v>1491268000</v>
+        <v>1632404000</v>
       </c>
       <c r="L3" t="n">
-        <v>-635219000</v>
+        <v>-418407000</v>
       </c>
       <c r="M3" t="n">
-        <v>763559000</v>
+        <v>588814000</v>
       </c>
       <c r="N3" t="n">
-        <v>128340000</v>
+        <v>170407000</v>
       </c>
       <c r="O3" t="n">
-        <v>362175432.219472</v>
+        <v>227909641.331366</v>
       </c>
       <c r="P3" t="n">
-        <v>95517000</v>
+        <v>101599000</v>
       </c>
       <c r="Q3" t="n">
-        <v>22497420000</v>
+        <v>19467879000</v>
       </c>
       <c r="R3" t="n">
-        <v>1370821000</v>
+        <v>1599719000</v>
       </c>
       <c r="S3" t="n">
         <v>1635291000</v>
@@ -874,147 +876,147 @@
         <v>1635291000</v>
       </c>
       <c r="U3" t="n">
-        <v>0.058</v>
+        <v>0.062</v>
       </c>
       <c r="V3" t="n">
-        <v>0.058</v>
+        <v>0.062</v>
       </c>
       <c r="W3" t="n">
-        <v>95517000</v>
+        <v>101599000</v>
       </c>
       <c r="X3" t="n">
-        <v>95517000</v>
+        <v>101599000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>95517000</v>
+        <v>101599000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-519719000</v>
+        <v>-542612000</v>
       </c>
       <c r="AB3" t="n">
-        <v>615236000</v>
+        <v>644211000</v>
       </c>
       <c r="AC3" t="n">
-        <v>615236000</v>
+        <v>644211000</v>
       </c>
       <c r="AD3" t="n">
-        <v>112473000</v>
+        <v>399379000</v>
       </c>
       <c r="AE3" t="n">
-        <v>727709000</v>
+        <v>1043590000</v>
       </c>
       <c r="AF3" t="n">
-        <v>22341000</v>
+        <v>23027000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-306455000</v>
+        <v>-230020000</v>
       </c>
       <c r="AH3" t="n">
-        <v>6418000</v>
+        <v>-1123000</v>
       </c>
       <c r="AI3" t="n">
-        <v>295106000</v>
+        <v>212812000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4931000</v>
+        <v>18331000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-635219000</v>
+        <v>-418407000</v>
       </c>
       <c r="AL3" t="n">
-        <v>763559000</v>
+        <v>588814000</v>
       </c>
       <c r="AM3" t="n">
-        <v>128340000</v>
+        <v>170407000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1579728000</v>
+        <v>1611775000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1815057000</v>
+        <v>1651457000</v>
       </c>
       <c r="AP3" t="n">
-        <v>904473000</v>
+        <v>744816000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1093596000</v>
+        <v>1036978000</v>
       </c>
       <c r="AR3" t="n">
-        <v>532167000</v>
+        <v>479184000</v>
       </c>
       <c r="AS3" t="n">
-        <v>561429000</v>
+        <v>557794000</v>
       </c>
       <c r="AT3" t="n">
-        <v>3394785000</v>
+        <v>3263232000</v>
       </c>
       <c r="AU3" t="n">
-        <v>20682363000</v>
+        <v>17816422000</v>
       </c>
       <c r="AV3" t="n">
-        <v>24077148000</v>
+        <v>21079654000</v>
       </c>
       <c r="AW3" t="n">
-        <v>24077148000</v>
+        <v>21079654000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-78306358.668634</v>
+        <v>-48748567.780528</v>
       </c>
       <c r="C4" t="n">
-        <v>0.382697</v>
+        <v>0.154558</v>
       </c>
       <c r="D4" t="n">
-        <v>2261704000</v>
+        <v>2354263000</v>
       </c>
       <c r="E4" t="n">
-        <v>-204617000</v>
+        <v>-315407000</v>
       </c>
       <c r="F4" t="n">
-        <v>-204617000</v>
+        <v>-315407000</v>
       </c>
       <c r="G4" t="n">
-        <v>101599000</v>
+        <v>95517000</v>
       </c>
       <c r="H4" t="n">
-        <v>424683000</v>
+        <v>547588000</v>
       </c>
       <c r="I4" t="n">
-        <v>17816422000</v>
+        <v>20682363000</v>
       </c>
       <c r="J4" t="n">
-        <v>2057087000</v>
+        <v>2038856000</v>
       </c>
       <c r="K4" t="n">
-        <v>1632404000</v>
+        <v>1491268000</v>
       </c>
       <c r="L4" t="n">
-        <v>-418407000</v>
+        <v>-635219000</v>
       </c>
       <c r="M4" t="n">
-        <v>588814000</v>
+        <v>763559000</v>
       </c>
       <c r="N4" t="n">
-        <v>170407000</v>
+        <v>128340000</v>
       </c>
       <c r="O4" t="n">
-        <v>227909641.331366</v>
+        <v>362175432.219472</v>
       </c>
       <c r="P4" t="n">
-        <v>101599000</v>
+        <v>95517000</v>
       </c>
       <c r="Q4" t="n">
-        <v>19467879000</v>
+        <v>22497420000</v>
       </c>
       <c r="R4" t="n">
-        <v>1599719000</v>
+        <v>1370821000</v>
       </c>
       <c r="S4" t="n">
         <v>1635291000</v>
@@ -1023,147 +1025,147 @@
         <v>1635291000</v>
       </c>
       <c r="U4" t="n">
-        <v>0.062</v>
+        <v>0.058</v>
       </c>
       <c r="V4" t="n">
-        <v>0.062</v>
+        <v>0.058</v>
       </c>
       <c r="W4" t="n">
-        <v>101599000</v>
+        <v>95517000</v>
       </c>
       <c r="X4" t="n">
-        <v>101599000</v>
+        <v>95517000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>101599000</v>
+        <v>95517000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-542612000</v>
+        <v>-519719000</v>
       </c>
       <c r="AB4" t="n">
-        <v>644211000</v>
+        <v>615236000</v>
       </c>
       <c r="AC4" t="n">
-        <v>644211000</v>
+        <v>615236000</v>
       </c>
       <c r="AD4" t="n">
-        <v>399379000</v>
+        <v>112473000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1043590000</v>
+        <v>727709000</v>
       </c>
       <c r="AF4" t="n">
-        <v>23027000</v>
+        <v>22341000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-230020000</v>
+        <v>-306455000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1123000</v>
+        <v>6418000</v>
       </c>
       <c r="AI4" t="n">
-        <v>212812000</v>
+        <v>295106000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18331000</v>
+        <v>4931000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-418407000</v>
+        <v>-635219000</v>
       </c>
       <c r="AL4" t="n">
-        <v>588814000</v>
+        <v>763559000</v>
       </c>
       <c r="AM4" t="n">
-        <v>170407000</v>
+        <v>128340000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1611775000</v>
+        <v>1579728000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1651457000</v>
+        <v>1815057000</v>
       </c>
       <c r="AP4" t="n">
-        <v>744816000</v>
+        <v>904473000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1036978000</v>
+        <v>1093596000</v>
       </c>
       <c r="AR4" t="n">
-        <v>479184000</v>
+        <v>532167000</v>
       </c>
       <c r="AS4" t="n">
-        <v>557794000</v>
+        <v>561429000</v>
       </c>
       <c r="AT4" t="n">
-        <v>3263232000</v>
+        <v>3394785000</v>
       </c>
       <c r="AU4" t="n">
-        <v>17816422000</v>
+        <v>20682363000</v>
       </c>
       <c r="AV4" t="n">
-        <v>21079654000</v>
+        <v>24077148000</v>
       </c>
       <c r="AW4" t="n">
-        <v>21079654000</v>
+        <v>24077148000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-3180696.038547</v>
+        <v>-1711928250</v>
       </c>
       <c r="C5" t="n">
-        <v>0.14391</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>2313699000</v>
+        <v>2589296000</v>
       </c>
       <c r="E5" t="n">
-        <v>-22102000</v>
+        <v>-6847441000</v>
       </c>
       <c r="F5" t="n">
-        <v>-22102000</v>
+        <v>-6847713000</v>
       </c>
       <c r="G5" t="n">
-        <v>1315245000</v>
+        <v>-6556733000</v>
       </c>
       <c r="H5" t="n">
-        <v>426425000</v>
+        <v>768838000</v>
       </c>
       <c r="I5" t="n">
-        <v>17022216000</v>
+        <v>18787323000</v>
       </c>
       <c r="J5" t="n">
-        <v>2291597000</v>
+        <v>-4258145000</v>
       </c>
       <c r="K5" t="n">
-        <v>1865172000</v>
+        <v>-5026983000</v>
       </c>
       <c r="L5" t="n">
-        <v>-37921000</v>
+        <v>-610766000</v>
       </c>
       <c r="M5" t="n">
-        <v>233498000</v>
+        <v>726262000</v>
       </c>
       <c r="N5" t="n">
-        <v>195577000</v>
+        <v>115496000</v>
       </c>
       <c r="O5" t="n">
-        <v>1334166303.961453</v>
+        <v>-1420676250</v>
       </c>
       <c r="P5" t="n">
-        <v>1315245000</v>
+        <v>-6556733000</v>
       </c>
       <c r="Q5" t="n">
-        <v>18467007000</v>
+        <v>20430185000</v>
       </c>
       <c r="R5" t="n">
-        <v>1826666000</v>
+        <v>-5141118000</v>
       </c>
       <c r="S5" t="n">
         <v>1635291000</v>
@@ -1171,92 +1173,90 @@
       <c r="T5" t="n">
         <v>1635291000</v>
       </c>
-      <c r="U5" t="n">
-        <v>0.804</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.804</v>
+        <v>-4.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1315245000</v>
+        <v>-6556733000</v>
       </c>
       <c r="X5" t="n">
-        <v>1315245000</v>
+        <v>-6556733000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1315245000</v>
+        <v>-6556733000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-81615000</v>
+        <v>-625205000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1396860000</v>
+        <v>-5931528000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1396860000</v>
+        <v>-5931528000</v>
       </c>
       <c r="AD5" t="n">
-        <v>234814000</v>
+        <v>178283000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1631674000</v>
+        <v>-5753245000</v>
       </c>
       <c r="AF5" t="n">
-        <v>21331000</v>
+        <v>29359000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-50786000</v>
+        <v>-6855449000</v>
       </c>
       <c r="AH5" t="n">
-        <v>11377000</v>
+        <v>-9661000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-42823000</v>
+        <v>6870948000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>82232000</v>
+        <v>-6110000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-37921000</v>
+        <v>-610766000</v>
       </c>
       <c r="AL5" t="n">
-        <v>233498000</v>
+        <v>726262000</v>
       </c>
       <c r="AM5" t="n">
-        <v>195577000</v>
+        <v>115496000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1743519000</v>
+        <v>1645285000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1444791000</v>
+        <v>1642862000</v>
       </c>
       <c r="AP5" t="n">
-        <v>667782000</v>
+        <v>809474000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>910303000</v>
+        <v>1126315000</v>
       </c>
       <c r="AR5" t="n">
-        <v>430244000</v>
+        <v>541984000</v>
       </c>
       <c r="AS5" t="n">
-        <v>480059000</v>
+        <v>584331000</v>
       </c>
       <c r="AT5" t="n">
-        <v>3188310000</v>
+        <v>3288147000</v>
       </c>
       <c r="AU5" t="n">
-        <v>17022216000</v>
+        <v>18787323000</v>
       </c>
       <c r="AV5" t="n">
-        <v>20210526000</v>
+        <v>22075470000</v>
       </c>
       <c r="AW5" t="n">
-        <v>20210526000</v>
+        <v>22075470000</v>
       </c>
     </row>
   </sheetData>
@@ -1632,56 +1632,50 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1635291556</v>
+        <v>1635291000</v>
       </c>
       <c r="C2" t="n">
-        <v>1635291556</v>
+        <v>1635291000</v>
       </c>
       <c r="D2" t="n">
-        <v>5292126000</v>
+        <v>713933000</v>
       </c>
       <c r="E2" t="n">
-        <v>9166345000</v>
+        <v>3998099000</v>
       </c>
       <c r="F2" t="n">
-        <v>7623177000</v>
+        <v>12694186000</v>
       </c>
       <c r="G2" t="n">
-        <v>17566431000</v>
+        <v>17397294000</v>
       </c>
       <c r="H2" t="n">
-        <v>6033783000</v>
+        <v>6101192000</v>
       </c>
       <c r="I2" t="n">
-        <v>7623177000</v>
+        <v>12694186000</v>
       </c>
       <c r="J2" t="n">
-        <v>8400086000</v>
+        <v>13399195000</v>
       </c>
       <c r="K2" t="n">
-        <v>13328648000</v>
+        <v>13399195000</v>
       </c>
       <c r="L2" t="n">
-        <v>12559285000</v>
+        <v>13768035000</v>
       </c>
       <c r="M2" t="n">
-        <v>4159199000</v>
+        <v>368840000</v>
       </c>
       <c r="N2" t="n">
-        <v>8400086000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>547674000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1196770000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3705495000</v>
-      </c>
+        <v>13399195000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>119218000</v>
       </c>
@@ -1689,162 +1683,164 @@
         <v>119218000</v>
       </c>
       <c r="T2" t="n">
-        <v>25150002000</v>
+        <v>15872439000</v>
       </c>
       <c r="U2" t="n">
-        <v>6997029000</v>
+        <v>1150836000</v>
       </c>
       <c r="V2" t="n">
-        <v>675359000</v>
+        <v>200477000</v>
       </c>
       <c r="W2" t="n">
-        <v>133089000</v>
+        <v>101575000</v>
       </c>
       <c r="X2" t="n">
-        <v>4928562000</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>4928562000</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1260019000</v>
+        <v>848784000</v>
       </c>
       <c r="AA2" t="n">
-        <v>18152973000</v>
+        <v>14721603000</v>
       </c>
       <c r="AB2" t="n">
-        <v>4237783000</v>
+        <v>3998099000</v>
       </c>
       <c r="AC2" t="n">
-        <v>4237783000</v>
+        <v>3998099000</v>
       </c>
       <c r="AD2" t="n">
-        <v>908794000</v>
+        <v>863250000</v>
       </c>
       <c r="AE2" t="n">
-        <v>10933794000</v>
+        <v>8897586000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1335119000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>1954402000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>89002000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>226782000</v>
+        <v>256378000</v>
       </c>
       <c r="AI2" t="n">
-        <v>9371893000</v>
+        <v>6597804000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>37709287000</v>
+        <v>29640474000</v>
       </c>
       <c r="AK2" t="n">
-        <v>13522531000</v>
+        <v>8817679000</v>
       </c>
       <c r="AL2" t="n">
-        <v>557059000</v>
+        <v>378938000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1745792000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>2989668000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>608921000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>1322492000</v>
+        <v>2016947000</v>
       </c>
       <c r="AP2" t="n">
-        <v>423300000</v>
+        <v>363800000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>209936000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>209936000</v>
-      </c>
+        <v>223783000</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>776909000</v>
+        <v>705009000</v>
       </c>
       <c r="AT2" t="n">
-        <v>750767000</v>
+        <v>678595000</v>
       </c>
       <c r="AU2" t="n">
-        <v>26142000</v>
+        <v>26414000</v>
       </c>
       <c r="AV2" t="n">
-        <v>10232835000</v>
+        <v>4520281000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-6268681000</v>
+        <v>-4738475000</v>
       </c>
       <c r="AX2" t="n">
-        <v>16501516000</v>
+        <v>9258756000</v>
       </c>
       <c r="AY2" t="n">
-        <v>2057480000</v>
+        <v>1118496000</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>11047359000</v>
+        <v>6260270000</v>
       </c>
       <c r="BB2" t="n">
-        <v>65453000</v>
+        <v>40309000</v>
       </c>
       <c r="BC2" t="n">
-        <v>3331224000</v>
+        <v>1839681000</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>24186756000</v>
+        <v>20822795000</v>
       </c>
       <c r="BF2" t="n">
-        <v>2810765000</v>
+        <v>1897477000</v>
       </c>
       <c r="BG2" t="n">
-        <v>380470000</v>
+        <v>1332917000</v>
       </c>
       <c r="BH2" t="n">
-        <v>6052537000</v>
+        <v>5206919000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2544658000</v>
+        <v>2070648000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>2730087000</v>
+        <v>2570242000</v>
       </c>
       <c r="BK2" t="n">
-        <v>777792000</v>
+        <v>566029000</v>
       </c>
       <c r="BL2" t="n">
-        <v>989641000</v>
+        <v>860270000</v>
       </c>
       <c r="BM2" t="n">
-        <v>463728000</v>
+        <v>133286000</v>
       </c>
       <c r="BN2" t="n">
-        <v>6260506000</v>
+        <v>4610234000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-3822183000</v>
+        <v>-562597000</v>
       </c>
       <c r="BP2" t="n">
-        <v>10082689000</v>
+        <v>5172831000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7229109000</v>
+        <v>6781692000</v>
       </c>
       <c r="BR2" t="n">
-        <v>3354890000</v>
+        <v>3497526000</v>
       </c>
       <c r="BS2" t="n">
-        <v>3874219000</v>
+        <v>3284166000</v>
       </c>
       <c r="BT2" t="n">
-        <v>3874219000</v>
+        <v>3284166000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1635291000</v>
@@ -1853,43 +1849,43 @@
         <v>1635291000</v>
       </c>
       <c r="D3" t="n">
-        <v>3866694000</v>
+        <v>3459067000</v>
       </c>
       <c r="E3" t="n">
-        <v>9494585000</v>
+        <v>7842584000</v>
       </c>
       <c r="F3" t="n">
-        <v>9527847000</v>
+        <v>9773253000</v>
       </c>
       <c r="G3" t="n">
-        <v>19767895000</v>
+        <v>18318535000</v>
       </c>
       <c r="H3" t="n">
-        <v>7553195000</v>
+        <v>7530918000</v>
       </c>
       <c r="I3" t="n">
-        <v>9527847000</v>
+        <v>9773253000</v>
       </c>
       <c r="J3" t="n">
-        <v>10273310000</v>
+        <v>10475951000</v>
       </c>
       <c r="K3" t="n">
-        <v>14731274000</v>
+        <v>13661123000</v>
       </c>
       <c r="L3" t="n">
-        <v>13912224000</v>
+        <v>13594570000</v>
       </c>
       <c r="M3" t="n">
-        <v>3638914000</v>
+        <v>3118619000</v>
       </c>
       <c r="N3" t="n">
-        <v>10273310000</v>
+        <v>10475951000</v>
       </c>
       <c r="O3" t="n">
         <v>547674000</v>
       </c>
       <c r="P3" t="n">
-        <v>7789730000</v>
+        <v>7779651000</v>
       </c>
       <c r="Q3" t="n">
         <v>3705495000</v>
@@ -1901,162 +1897,168 @@
         <v>119218000</v>
       </c>
       <c r="T3" t="n">
-        <v>27788171000</v>
+        <v>28039883000</v>
       </c>
       <c r="U3" t="n">
-        <v>6184508000</v>
+        <v>4718560000</v>
       </c>
       <c r="V3" t="n">
-        <v>475164000</v>
+        <v>303077000</v>
       </c>
       <c r="W3" t="n">
-        <v>126910000</v>
+        <v>115582000</v>
       </c>
       <c r="X3" t="n">
-        <v>4457964000</v>
+        <v>3185172000</v>
       </c>
       <c r="Y3" t="n">
-        <v>4457964000</v>
+        <v>3185172000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1124470000</v>
+        <v>1114729000</v>
       </c>
       <c r="AA3" t="n">
-        <v>21603663000</v>
+        <v>23321323000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5036621000</v>
+        <v>4657412000</v>
       </c>
       <c r="AC3" t="n">
-        <v>5036621000</v>
+        <v>4657412000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1144479000</v>
+        <v>988395000</v>
       </c>
       <c r="AE3" t="n">
-        <v>8615609000</v>
+        <v>11498049000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1087308000</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>1129191000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
       <c r="AH3" t="n">
-        <v>181935000</v>
+        <v>303977000</v>
       </c>
       <c r="AI3" t="n">
-        <v>7346366000</v>
+        <v>10064881000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>41700395000</v>
+        <v>41634453000</v>
       </c>
       <c r="AK3" t="n">
-        <v>12543537000</v>
+        <v>10782212000</v>
       </c>
       <c r="AL3" t="n">
-        <v>905494000</v>
+        <v>728894000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1701827000</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>2000695000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
       <c r="AO3" t="n">
-        <v>1290427000</v>
+        <v>1613095000</v>
       </c>
       <c r="AP3" t="n">
-        <v>411400000</v>
+        <v>387600000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>196297000</v>
+        <v>220023000</v>
       </c>
       <c r="AR3" t="n">
-        <v>196297000</v>
+        <v>220023000</v>
       </c>
       <c r="AS3" t="n">
-        <v>745463000</v>
+        <v>702698000</v>
       </c>
       <c r="AT3" t="n">
-        <v>719049000</v>
+        <v>676284000</v>
       </c>
       <c r="AU3" t="n">
         <v>26414000</v>
       </c>
       <c r="AV3" t="n">
-        <v>8994456000</v>
+        <v>7129902000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-5566120000</v>
+        <v>-5087971000</v>
       </c>
       <c r="AX3" t="n">
-        <v>14560576000</v>
+        <v>12217873000</v>
       </c>
       <c r="AY3" t="n">
-        <v>2553301000</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
+        <v>2393382000</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>7800296000</v>
+      </c>
       <c r="BA3" t="n">
-        <v>9151336000</v>
+        <v>6987584000</v>
       </c>
       <c r="BB3" t="n">
-        <v>57777000</v>
+        <v>40599000</v>
       </c>
       <c r="BC3" t="n">
-        <v>2798162000</v>
+        <v>2796308000</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>29156858000</v>
+        <v>30852241000</v>
       </c>
       <c r="BF3" t="n">
-        <v>3562398000</v>
+        <v>4897224000</v>
       </c>
       <c r="BG3" t="n">
-        <v>1596936000</v>
+        <v>1855636000</v>
       </c>
       <c r="BH3" t="n">
-        <v>6544851000</v>
+        <v>6928601000</v>
       </c>
       <c r="BI3" t="n">
-        <v>3041544000</v>
+        <v>2237250000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>2677781000</v>
+        <v>3712196000</v>
       </c>
       <c r="BK3" t="n">
-        <v>825526000</v>
+        <v>979155000</v>
       </c>
       <c r="BL3" t="n">
-        <v>1043809000</v>
+        <v>1092041000</v>
       </c>
       <c r="BM3" t="n">
-        <v>433775000</v>
+        <v>249526000</v>
       </c>
       <c r="BN3" t="n">
-        <v>8532510000</v>
+        <v>7211885000</v>
       </c>
       <c r="BO3" t="n">
-        <v>-650026000</v>
+        <v>-670460000</v>
       </c>
       <c r="BP3" t="n">
-        <v>9182536000</v>
+        <v>7882345000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7442579000</v>
+        <v>8617328000</v>
       </c>
       <c r="BR3" t="n">
-        <v>1814688000</v>
+        <v>4233811000</v>
       </c>
       <c r="BS3" t="n">
-        <v>5627891000</v>
+        <v>4383517000</v>
       </c>
       <c r="BT3" t="n">
-        <v>5627891000</v>
+        <v>4383517000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1635291000</v>
@@ -2065,43 +2067,43 @@
         <v>1635291000</v>
       </c>
       <c r="D4" t="n">
-        <v>3459067000</v>
+        <v>3866694000</v>
       </c>
       <c r="E4" t="n">
-        <v>7842584000</v>
+        <v>9494585000</v>
       </c>
       <c r="F4" t="n">
-        <v>9773253000</v>
+        <v>9527847000</v>
       </c>
       <c r="G4" t="n">
-        <v>18318535000</v>
+        <v>19767895000</v>
       </c>
       <c r="H4" t="n">
-        <v>7530918000</v>
+        <v>7553195000</v>
       </c>
       <c r="I4" t="n">
-        <v>9773253000</v>
+        <v>9527847000</v>
       </c>
       <c r="J4" t="n">
-        <v>10475951000</v>
+        <v>10273310000</v>
       </c>
       <c r="K4" t="n">
-        <v>13661123000</v>
+        <v>14731274000</v>
       </c>
       <c r="L4" t="n">
-        <v>13594570000</v>
+        <v>13912224000</v>
       </c>
       <c r="M4" t="n">
-        <v>3118619000</v>
+        <v>3638914000</v>
       </c>
       <c r="N4" t="n">
-        <v>10475951000</v>
+        <v>10273310000</v>
       </c>
       <c r="O4" t="n">
         <v>547674000</v>
       </c>
       <c r="P4" t="n">
-        <v>7779651000</v>
+        <v>7789730000</v>
       </c>
       <c r="Q4" t="n">
         <v>3705495000</v>
@@ -2113,211 +2115,211 @@
         <v>119218000</v>
       </c>
       <c r="T4" t="n">
-        <v>28039883000</v>
+        <v>27788171000</v>
       </c>
       <c r="U4" t="n">
-        <v>4718560000</v>
+        <v>6184508000</v>
       </c>
       <c r="V4" t="n">
-        <v>303077000</v>
+        <v>475164000</v>
       </c>
       <c r="W4" t="n">
-        <v>115582000</v>
+        <v>126910000</v>
       </c>
       <c r="X4" t="n">
-        <v>3185172000</v>
+        <v>4457964000</v>
       </c>
       <c r="Y4" t="n">
-        <v>3185172000</v>
+        <v>4457964000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1114729000</v>
+        <v>1124470000</v>
       </c>
       <c r="AA4" t="n">
-        <v>23321323000</v>
+        <v>21603663000</v>
       </c>
       <c r="AB4" t="n">
-        <v>4657412000</v>
+        <v>5036621000</v>
       </c>
       <c r="AC4" t="n">
-        <v>4657412000</v>
+        <v>5036621000</v>
       </c>
       <c r="AD4" t="n">
-        <v>988395000</v>
+        <v>1144479000</v>
       </c>
       <c r="AE4" t="n">
-        <v>11498049000</v>
+        <v>8615609000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1129191000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
+        <v>1087308000</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>303977000</v>
+        <v>181935000</v>
       </c>
       <c r="AI4" t="n">
-        <v>10064881000</v>
+        <v>7346366000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>41634453000</v>
+        <v>41700395000</v>
       </c>
       <c r="AK4" t="n">
-        <v>10782212000</v>
+        <v>12543537000</v>
       </c>
       <c r="AL4" t="n">
-        <v>728894000</v>
+        <v>905494000</v>
       </c>
       <c r="AM4" t="n">
-        <v>2000695000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
+        <v>1701827000</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>1613095000</v>
+        <v>1290427000</v>
       </c>
       <c r="AP4" t="n">
-        <v>387600000</v>
+        <v>411400000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>220023000</v>
+        <v>196297000</v>
       </c>
       <c r="AR4" t="n">
-        <v>220023000</v>
+        <v>196297000</v>
       </c>
       <c r="AS4" t="n">
-        <v>702698000</v>
+        <v>745463000</v>
       </c>
       <c r="AT4" t="n">
-        <v>676284000</v>
+        <v>719049000</v>
       </c>
       <c r="AU4" t="n">
         <v>26414000</v>
       </c>
       <c r="AV4" t="n">
-        <v>7129902000</v>
+        <v>8994456000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-5087971000</v>
+        <v>-5566120000</v>
       </c>
       <c r="AX4" t="n">
-        <v>12217873000</v>
+        <v>14560576000</v>
       </c>
       <c r="AY4" t="n">
-        <v>2393382000</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>7800296000</v>
-      </c>
+        <v>2553301000</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>6987584000</v>
+        <v>9151336000</v>
       </c>
       <c r="BB4" t="n">
-        <v>40599000</v>
+        <v>57777000</v>
       </c>
       <c r="BC4" t="n">
-        <v>2796308000</v>
+        <v>2798162000</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>30852241000</v>
+        <v>29156858000</v>
       </c>
       <c r="BF4" t="n">
-        <v>4897224000</v>
+        <v>3562398000</v>
       </c>
       <c r="BG4" t="n">
-        <v>1855636000</v>
+        <v>1596936000</v>
       </c>
       <c r="BH4" t="n">
-        <v>6928601000</v>
+        <v>6544851000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2237250000</v>
+        <v>3041544000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3712196000</v>
+        <v>2677781000</v>
       </c>
       <c r="BK4" t="n">
-        <v>979155000</v>
+        <v>825526000</v>
       </c>
       <c r="BL4" t="n">
-        <v>1092041000</v>
+        <v>1043809000</v>
       </c>
       <c r="BM4" t="n">
-        <v>249526000</v>
+        <v>433775000</v>
       </c>
       <c r="BN4" t="n">
-        <v>7211885000</v>
+        <v>8532510000</v>
       </c>
       <c r="BO4" t="n">
-        <v>-670460000</v>
+        <v>-650026000</v>
       </c>
       <c r="BP4" t="n">
-        <v>7882345000</v>
+        <v>9182536000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8617328000</v>
+        <v>7442579000</v>
       </c>
       <c r="BR4" t="n">
-        <v>4233811000</v>
+        <v>1814688000</v>
       </c>
       <c r="BS4" t="n">
-        <v>4383517000</v>
+        <v>5627891000</v>
       </c>
       <c r="BT4" t="n">
-        <v>4383517000</v>
+        <v>5627891000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1635291000</v>
+        <v>1635291556</v>
       </c>
       <c r="C5" t="n">
-        <v>1635291000</v>
+        <v>1635291556</v>
       </c>
       <c r="D5" t="n">
-        <v>713933000</v>
+        <v>5292126000</v>
       </c>
       <c r="E5" t="n">
-        <v>3998099000</v>
+        <v>9166345000</v>
       </c>
       <c r="F5" t="n">
-        <v>12694186000</v>
+        <v>7623177000</v>
       </c>
       <c r="G5" t="n">
-        <v>17397294000</v>
+        <v>17566431000</v>
       </c>
       <c r="H5" t="n">
-        <v>6101192000</v>
+        <v>6033783000</v>
       </c>
       <c r="I5" t="n">
-        <v>12694186000</v>
+        <v>7623177000</v>
       </c>
       <c r="J5" t="n">
-        <v>13399195000</v>
+        <v>8400086000</v>
       </c>
       <c r="K5" t="n">
-        <v>13399195000</v>
+        <v>13328648000</v>
       </c>
       <c r="L5" t="n">
-        <v>13768035000</v>
+        <v>12559285000</v>
       </c>
       <c r="M5" t="n">
-        <v>368840000</v>
+        <v>4159199000</v>
       </c>
       <c r="N5" t="n">
-        <v>13399195000</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+        <v>8400086000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>547674000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1196770000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3705495000</v>
+      </c>
       <c r="R5" t="n">
         <v>119218000</v>
       </c>
@@ -2325,159 +2327,157 @@
         <v>119218000</v>
       </c>
       <c r="T5" t="n">
-        <v>15872439000</v>
+        <v>25150002000</v>
       </c>
       <c r="U5" t="n">
-        <v>1150836000</v>
+        <v>6997029000</v>
       </c>
       <c r="V5" t="n">
-        <v>200477000</v>
+        <v>675359000</v>
       </c>
       <c r="W5" t="n">
-        <v>101575000</v>
+        <v>133089000</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>4928562000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>4928562000</v>
       </c>
       <c r="Z5" t="n">
-        <v>848784000</v>
+        <v>1260019000</v>
       </c>
       <c r="AA5" t="n">
-        <v>14721603000</v>
+        <v>18152973000</v>
       </c>
       <c r="AB5" t="n">
-        <v>3998099000</v>
+        <v>4237783000</v>
       </c>
       <c r="AC5" t="n">
-        <v>3998099000</v>
+        <v>4237783000</v>
       </c>
       <c r="AD5" t="n">
-        <v>863250000</v>
+        <v>908794000</v>
       </c>
       <c r="AE5" t="n">
-        <v>8897586000</v>
+        <v>10933794000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1954402000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>89002000</v>
-      </c>
+        <v>1335119000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>256378000</v>
+        <v>226782000</v>
       </c>
       <c r="AI5" t="n">
-        <v>6597804000</v>
+        <v>9371893000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>29640474000</v>
+        <v>37709287000</v>
       </c>
       <c r="AK5" t="n">
-        <v>8817679000</v>
+        <v>13522531000</v>
       </c>
       <c r="AL5" t="n">
-        <v>378938000</v>
+        <v>557059000</v>
       </c>
       <c r="AM5" t="n">
-        <v>2989668000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>608921000</v>
-      </c>
+        <v>1745792000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>2016947000</v>
+        <v>1322492000</v>
       </c>
       <c r="AP5" t="n">
-        <v>363800000</v>
+        <v>423300000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>223783000</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+        <v>209936000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>209936000</v>
+      </c>
       <c r="AS5" t="n">
-        <v>705009000</v>
+        <v>776909000</v>
       </c>
       <c r="AT5" t="n">
-        <v>678595000</v>
+        <v>750767000</v>
       </c>
       <c r="AU5" t="n">
-        <v>26414000</v>
+        <v>26142000</v>
       </c>
       <c r="AV5" t="n">
-        <v>4520281000</v>
+        <v>10232835000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-4738475000</v>
+        <v>-6268681000</v>
       </c>
       <c r="AX5" t="n">
-        <v>9258756000</v>
+        <v>16501516000</v>
       </c>
       <c r="AY5" t="n">
-        <v>1118496000</v>
+        <v>2057480000</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>6260270000</v>
+        <v>11047359000</v>
       </c>
       <c r="BB5" t="n">
-        <v>40309000</v>
+        <v>65453000</v>
       </c>
       <c r="BC5" t="n">
-        <v>1839681000</v>
+        <v>3331224000</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>20822795000</v>
+        <v>24186756000</v>
       </c>
       <c r="BF5" t="n">
-        <v>1897477000</v>
+        <v>2810765000</v>
       </c>
       <c r="BG5" t="n">
-        <v>1332917000</v>
+        <v>380470000</v>
       </c>
       <c r="BH5" t="n">
-        <v>5206919000</v>
+        <v>6052537000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2070648000</v>
+        <v>2544658000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>2570242000</v>
+        <v>2730087000</v>
       </c>
       <c r="BK5" t="n">
-        <v>566029000</v>
+        <v>777792000</v>
       </c>
       <c r="BL5" t="n">
-        <v>860270000</v>
+        <v>989641000</v>
       </c>
       <c r="BM5" t="n">
-        <v>133286000</v>
+        <v>463728000</v>
       </c>
       <c r="BN5" t="n">
-        <v>4610234000</v>
+        <v>6260506000</v>
       </c>
       <c r="BO5" t="n">
-        <v>-562597000</v>
+        <v>-3822183000</v>
       </c>
       <c r="BP5" t="n">
-        <v>5172831000</v>
+        <v>10082689000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6781692000</v>
+        <v>7229109000</v>
       </c>
       <c r="BR5" t="n">
-        <v>3497526000</v>
+        <v>3354890000</v>
       </c>
       <c r="BS5" t="n">
-        <v>3284166000</v>
+        <v>3874219000</v>
       </c>
       <c r="BT5" t="n">
-        <v>3284166000</v>
+        <v>3874219000</v>
       </c>
     </row>
   </sheetData>
@@ -2728,560 +2728,560 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-2262278000</v>
+        <v>-2658513000</v>
       </c>
       <c r="C2" t="n">
-        <v>-6496568000</v>
+        <v>-3089000000</v>
       </c>
       <c r="D2" t="n">
-        <v>6568327000</v>
+        <v>4958129000</v>
       </c>
       <c r="E2" t="n">
-        <v>-2118901000</v>
+        <v>-1176139000</v>
       </c>
       <c r="F2" t="n">
-        <v>3874219000</v>
+        <v>3284166000</v>
       </c>
       <c r="G2" t="n">
-        <v>5627891000</v>
+        <v>2184334000</v>
       </c>
       <c r="H2" t="n">
-        <v>12368000</v>
+        <v>-32019000</v>
       </c>
       <c r="I2" t="n">
-        <v>-1766040000</v>
+        <v>1131851000</v>
       </c>
       <c r="J2" t="n">
-        <v>-516834000</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>2639595000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1000000000</v>
+      </c>
       <c r="L2" t="n">
-        <v>-486515000</v>
+        <v>-229534000</v>
       </c>
       <c r="M2" t="n">
-        <v>71759000</v>
+        <v>1869129000</v>
       </c>
       <c r="N2" t="n">
-        <v>71759000</v>
+        <v>1869129000</v>
       </c>
       <c r="O2" t="n">
-        <v>-6496568000</v>
+        <v>-3089000000</v>
       </c>
       <c r="P2" t="n">
-        <v>6568327000</v>
+        <v>4958129000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1105829000</v>
+        <v>-25370000</v>
       </c>
       <c r="R2" t="n">
-        <v>1048004000</v>
+        <v>-59563000</v>
       </c>
       <c r="S2" t="n">
-        <v>117252000</v>
+        <v>70842000</v>
       </c>
       <c r="T2" t="n">
-        <v>3712000</v>
+        <v>75207000</v>
       </c>
       <c r="U2" t="n">
-        <v>92000</v>
+        <v>401274000</v>
       </c>
       <c r="V2" t="n">
-        <v>20092000</v>
+        <v>761274000</v>
       </c>
       <c r="W2" t="n">
-        <v>-20000000</v>
+        <v>-360000000</v>
       </c>
       <c r="X2" t="n">
-        <v>-15000000</v>
+        <v>36413000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>51413000</v>
       </c>
       <c r="Z2" t="n">
         <v>-15000000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-2009889000</v>
+        <v>-1149897000</v>
       </c>
       <c r="AB2" t="n">
-        <v>109012000</v>
+        <v>26242000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2118901000</v>
+        <v>-1176139000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-143377000</v>
+        <v>-1482374000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-174198000</v>
+        <v>-343788000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2435589000</v>
+        <v>-3445203000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-115999000</v>
+        <v>-1379441000</v>
       </c>
       <c r="AH2" t="n">
-        <v>2051287000</v>
+        <v>248585000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-2233439000</v>
+        <v>-218884000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>414942000</v>
+        <v>-1669997000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-2452244000</v>
+        <v>-1186425000</v>
       </c>
       <c r="AL2" t="n">
-        <v>540454000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>17243000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>768838000</v>
+        <v>426425000</v>
       </c>
       <c r="AP2" t="n">
-        <v>768838000</v>
+        <v>426425000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-11448000</v>
+        <v>-53891000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-12370000</v>
+        <v>32019000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-9661000</v>
+        <v>-5196000</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>16573000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-5753245000</v>
+        <v>1631674000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-2135592000</v>
+        <v>-1720713000</v>
       </c>
       <c r="C3" t="n">
-        <v>-6255412000</v>
+        <v>-4688089000</v>
       </c>
       <c r="D3" t="n">
-        <v>7907413000</v>
+        <v>8282574000</v>
       </c>
       <c r="E3" t="n">
-        <v>-2487635000</v>
+        <v>-2627326000</v>
       </c>
       <c r="F3" t="n">
-        <v>5627891000</v>
+        <v>4383517000</v>
       </c>
       <c r="G3" t="n">
-        <v>4383517000</v>
+        <v>3284166000</v>
       </c>
       <c r="H3" t="n">
-        <v>17915000</v>
+        <v>77553000</v>
       </c>
       <c r="I3" t="n">
-        <v>1226459000</v>
+        <v>1021798000</v>
       </c>
       <c r="J3" t="n">
-        <v>1177766000</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
+        <v>5574544000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2461196000</v>
+      </c>
       <c r="L3" t="n">
-        <v>-474235000</v>
+        <v>-392135000</v>
       </c>
       <c r="M3" t="n">
-        <v>1652001000</v>
+        <v>3594485000</v>
       </c>
       <c r="N3" t="n">
-        <v>1652001000</v>
+        <v>3594485000</v>
       </c>
       <c r="O3" t="n">
-        <v>-6255412000</v>
+        <v>-4688089000</v>
       </c>
       <c r="P3" t="n">
-        <v>7907413000</v>
+        <v>8282574000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-303350000</v>
+        <v>-5459359000</v>
       </c>
       <c r="R3" t="n">
-        <v>1570843000</v>
+        <v>-2873918000</v>
       </c>
       <c r="S3" t="n">
-        <v>144840000</v>
+        <v>218666000</v>
       </c>
       <c r="T3" t="n">
-        <v>1105000</v>
+        <v>3005000</v>
       </c>
       <c r="U3" t="n">
-        <v>72266000</v>
+        <v>193269000</v>
       </c>
       <c r="V3" t="n">
-        <v>232266000</v>
+        <v>283269000</v>
       </c>
       <c r="W3" t="n">
-        <v>-160000000</v>
+        <v>-90000000</v>
       </c>
       <c r="X3" t="n">
-        <v>13000000</v>
+        <v>-6840000</v>
       </c>
       <c r="Y3" t="n">
-        <v>13000000</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-6840000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2419791000</v>
+        <v>-2608541000</v>
       </c>
       <c r="AB3" t="n">
-        <v>67844000</v>
+        <v>18785000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2487635000</v>
+        <v>-2627326000</v>
       </c>
       <c r="AD3" t="n">
-        <v>352043000</v>
+        <v>906613000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-337773000</v>
+        <v>-318986000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1544402000</v>
+        <v>-1066698000</v>
       </c>
       <c r="AG3" t="n">
-        <v>220884000</v>
+        <v>684269000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-2691111000</v>
+        <v>3523489000</v>
       </c>
       <c r="AI3" t="n">
-        <v>256377000</v>
+        <v>-608920000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>321152000</v>
+        <v>-1939314000</v>
       </c>
       <c r="AK3" t="n">
-        <v>182471000</v>
+        <v>-3117312000</v>
       </c>
       <c r="AL3" t="n">
-        <v>594974000</v>
+        <v>398247000</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>-9070000</v>
+        <v>119450000</v>
       </c>
       <c r="AO3" t="n">
-        <v>547588000</v>
+        <v>424683000</v>
       </c>
       <c r="AP3" t="n">
-        <v>547588000</v>
+        <v>424683000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7847000</v>
+        <v>-28408000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-17915000</v>
+        <v>-77553000</v>
       </c>
       <c r="AS3" t="n">
-        <v>780000</v>
+        <v>-1123000</v>
       </c>
       <c r="AT3" t="n">
-        <v>5638000</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>727709000</v>
+        <v>1043590000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1720713000</v>
+        <v>-2135592000</v>
       </c>
       <c r="C4" t="n">
-        <v>-4688089000</v>
+        <v>-6255412000</v>
       </c>
       <c r="D4" t="n">
-        <v>8282574000</v>
+        <v>7907413000</v>
       </c>
       <c r="E4" t="n">
-        <v>-2627326000</v>
+        <v>-2487635000</v>
       </c>
       <c r="F4" t="n">
+        <v>5627891000</v>
+      </c>
+      <c r="G4" t="n">
         <v>4383517000</v>
       </c>
-      <c r="G4" t="n">
-        <v>3284166000</v>
-      </c>
       <c r="H4" t="n">
-        <v>77553000</v>
+        <v>17915000</v>
       </c>
       <c r="I4" t="n">
-        <v>1021798000</v>
+        <v>1226459000</v>
       </c>
       <c r="J4" t="n">
-        <v>5574544000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2461196000</v>
-      </c>
+        <v>1177766000</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-392135000</v>
+        <v>-474235000</v>
       </c>
       <c r="M4" t="n">
-        <v>3594485000</v>
+        <v>1652001000</v>
       </c>
       <c r="N4" t="n">
-        <v>3594485000</v>
+        <v>1652001000</v>
       </c>
       <c r="O4" t="n">
-        <v>-4688089000</v>
+        <v>-6255412000</v>
       </c>
       <c r="P4" t="n">
-        <v>8282574000</v>
+        <v>7907413000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5459359000</v>
+        <v>-303350000</v>
       </c>
       <c r="R4" t="n">
-        <v>-2873918000</v>
+        <v>1570843000</v>
       </c>
       <c r="S4" t="n">
-        <v>218666000</v>
+        <v>144840000</v>
       </c>
       <c r="T4" t="n">
-        <v>3005000</v>
+        <v>1105000</v>
       </c>
       <c r="U4" t="n">
-        <v>193269000</v>
+        <v>72266000</v>
       </c>
       <c r="V4" t="n">
-        <v>283269000</v>
+        <v>232266000</v>
       </c>
       <c r="W4" t="n">
-        <v>-90000000</v>
+        <v>-160000000</v>
       </c>
       <c r="X4" t="n">
-        <v>-6840000</v>
+        <v>13000000</v>
       </c>
       <c r="Y4" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="Z4" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" t="n">
-        <v>-6840000</v>
-      </c>
       <c r="AA4" t="n">
-        <v>-2608541000</v>
+        <v>-2419791000</v>
       </c>
       <c r="AB4" t="n">
-        <v>18785000</v>
+        <v>67844000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2627326000</v>
+        <v>-2487635000</v>
       </c>
       <c r="AD4" t="n">
-        <v>906613000</v>
+        <v>352043000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-318986000</v>
+        <v>-337773000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1066698000</v>
+        <v>-1544402000</v>
       </c>
       <c r="AG4" t="n">
-        <v>684269000</v>
+        <v>220884000</v>
       </c>
       <c r="AH4" t="n">
-        <v>3523489000</v>
+        <v>-2691111000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-608920000</v>
+        <v>256377000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-1939314000</v>
+        <v>321152000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-3117312000</v>
+        <v>182471000</v>
       </c>
       <c r="AL4" t="n">
-        <v>398247000</v>
+        <v>594974000</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>119450000</v>
+        <v>-9070000</v>
       </c>
       <c r="AO4" t="n">
-        <v>424683000</v>
+        <v>547588000</v>
       </c>
       <c r="AP4" t="n">
-        <v>424683000</v>
+        <v>547588000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-28408000</v>
+        <v>7847000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-77553000</v>
+        <v>-17915000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1123000</v>
+        <v>780000</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>5638000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1043590000</v>
+        <v>727709000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-2658513000</v>
+        <v>-2262278000</v>
       </c>
       <c r="C5" t="n">
-        <v>-3089000000</v>
+        <v>-6496568000</v>
       </c>
       <c r="D5" t="n">
-        <v>4958129000</v>
+        <v>6568327000</v>
       </c>
       <c r="E5" t="n">
-        <v>-1176139000</v>
+        <v>-2118901000</v>
       </c>
       <c r="F5" t="n">
-        <v>3284166000</v>
+        <v>3874219000</v>
       </c>
       <c r="G5" t="n">
-        <v>2184334000</v>
+        <v>5627891000</v>
       </c>
       <c r="H5" t="n">
-        <v>-32019000</v>
+        <v>12368000</v>
       </c>
       <c r="I5" t="n">
-        <v>1131851000</v>
+        <v>-1766040000</v>
       </c>
       <c r="J5" t="n">
-        <v>2639595000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1000000000</v>
-      </c>
+        <v>-516834000</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-229534000</v>
+        <v>-486515000</v>
       </c>
       <c r="M5" t="n">
-        <v>1869129000</v>
+        <v>71759000</v>
       </c>
       <c r="N5" t="n">
-        <v>1869129000</v>
+        <v>71759000</v>
       </c>
       <c r="O5" t="n">
-        <v>-3089000000</v>
+        <v>-6496568000</v>
       </c>
       <c r="P5" t="n">
-        <v>4958129000</v>
+        <v>6568327000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-25370000</v>
+        <v>-1105829000</v>
       </c>
       <c r="R5" t="n">
-        <v>-59563000</v>
+        <v>1048004000</v>
       </c>
       <c r="S5" t="n">
-        <v>70842000</v>
+        <v>117252000</v>
       </c>
       <c r="T5" t="n">
-        <v>75207000</v>
+        <v>3712000</v>
       </c>
       <c r="U5" t="n">
-        <v>401274000</v>
+        <v>92000</v>
       </c>
       <c r="V5" t="n">
-        <v>761274000</v>
+        <v>20092000</v>
       </c>
       <c r="W5" t="n">
-        <v>-360000000</v>
+        <v>-20000000</v>
       </c>
       <c r="X5" t="n">
-        <v>36413000</v>
+        <v>-15000000</v>
       </c>
       <c r="Y5" t="n">
-        <v>51413000</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>-15000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1149897000</v>
+        <v>-2009889000</v>
       </c>
       <c r="AB5" t="n">
-        <v>26242000</v>
+        <v>109012000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1176139000</v>
+        <v>-2118901000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1482374000</v>
+        <v>-143377000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-343788000</v>
+        <v>-174198000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-3445203000</v>
+        <v>-2435589000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1379441000</v>
+        <v>-115999000</v>
       </c>
       <c r="AH5" t="n">
-        <v>248585000</v>
+        <v>2051287000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-218884000</v>
+        <v>-2233439000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-1669997000</v>
+        <v>414942000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1186425000</v>
+        <v>-2452244000</v>
       </c>
       <c r="AL5" t="n">
-        <v>17243000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
+        <v>540454000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>426425000</v>
+        <v>768838000</v>
       </c>
       <c r="AP5" t="n">
-        <v>426425000</v>
+        <v>768838000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-53891000</v>
+        <v>-11448000</v>
       </c>
       <c r="AR5" t="n">
-        <v>32019000</v>
+        <v>-12370000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-5196000</v>
+        <v>-9661000</v>
       </c>
       <c r="AT5" t="n">
-        <v>16573000</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>1631674000</v>
+        <v>-5753245000</v>
       </c>
     </row>
   </sheetData>
@@ -3295,7 +3295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ET2"/>
+  <dimension ref="A1:EQ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3371,680 +3371,665 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>fullTimeEmployees</t>
+          <t>companyOfficers</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>companyOfficers</t>
+          <t>auditRisk</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>auditRisk</t>
+          <t>boardRisk</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>boardRisk</t>
+          <t>compensationRisk</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>compensationRisk</t>
+          <t>shareHolderRightsRisk</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>shareHolderRightsRisk</t>
+          <t>overallRisk</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>overallRisk</t>
+          <t>governanceEpochDate</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>governanceEpochDate</t>
+          <t>executiveTeam</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>executiveTeam</t>
+          <t>maxAge</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>maxAge</t>
+          <t>priceHint</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>priceHint</t>
+          <t>previousClose</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>previousClose</t>
+          <t>open</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>dayLow</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>dayLow</t>
+          <t>dayHigh</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>dayHigh</t>
+          <t>regularMarketPreviousClose</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>regularMarketPreviousClose</t>
+          <t>regularMarketOpen</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>regularMarketOpen</t>
+          <t>regularMarketDayLow</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>regularMarketDayLow</t>
+          <t>regularMarketDayHigh</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>regularMarketDayHigh</t>
+          <t>exDividendDate</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>payoutRatio</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>fiveYearAvgDividendYield</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>fiveYearAvgDividendYield</t>
+          <t>trailingPE</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>forwardPE</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>forwardPE</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>bidSize</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>bidSize</t>
+          <t>askSize</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>askSize</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>forwardEps</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>forwardEps</t>
+          <t>pegRatio</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>pegRatio</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>region</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>shortName</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>longName</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>sourceInterval</t>
         </is>
       </c>
       <c r="DH1" t="inlineStr">
         <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
       <c r="EQ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4121,460 +4106,451 @@
           <t>China High Speed Transmission Equipment Group Co., Ltd. engages in the research, design, development, manufacture, and sale of various mechanical transmission equipment in the People's Republic of China, the United States, Europe, and internationally. It operates through four segments: Wind and Industrial Gear Transmission Equipment; Rail Transportation Gear Transmission Equipment; Trading Business; and Others. The company offers mechanical transmission equipment for use in wind power and a range of industrial applications; gear transmission equipment for use in rail transportation fields; and gears, gear boxes, and fittings. It engages in the trading of bulk commodity and steel industry chain; and provision of services for lighting, municipal landscape, and engineering procurement construction projects. China High Speed Transmission Equipment Group Co., Ltd. was founded in 1969 and is headquartered in Causeway Bay, Hong Kong. China High Speed Transmission Equipment Group Co., Ltd. operates as a subsidiary of Five Seasons XVI Limited.</t>
         </is>
       </c>
-      <c r="O2" t="n">
-        <v>8107</v>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>[{'maxAge': 1, 'name': 'Mr. Zubin  Li', 'age': 56, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1969, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ying  Seto', 'age': 49, 'title': 'CFO &amp; Company Secretary', 'yearBorn': 1976, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Xiaohong  Yuan', 'age': 49, 'title': 'Executive Director', 'yearBorn': 1976, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bo  Wang', 'age': 45, 'title': 'Executive Director', 'yearBorn': 1980, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
+      </c>
+      <c r="P2" t="n">
+        <v>10</v>
       </c>
       <c r="Q2" t="n">
         <v>10</v>
       </c>
       <c r="R2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T2" t="n">
         <v>10</v>
       </c>
-      <c r="S2" t="n">
-        <v>6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>9</v>
-      </c>
       <c r="U2" t="n">
-        <v>10</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1780272000</v>
-      </c>
-      <c r="W2" t="inlineStr">
+        <v>1780531200</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
+      <c r="W2" t="n">
+        <v>86400</v>
+      </c>
       <c r="X2" t="n">
-        <v>86400</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="n">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AB2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC2" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AE2" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.97</v>
+        <v>1590451200</v>
       </c>
       <c r="AH2" t="n">
-        <v>1590451200</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>9.733333999999999</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.6781609</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>3736000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>3736000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>703934</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>629600</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>629600</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS2" t="n">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2.2413793</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>6461000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>6461000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>729086</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.95</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
+        <v>2387525632</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2665525236</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.12098332</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.9436</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.82775</v>
+      </c>
+      <c r="BD2" t="n">
         <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3188818432</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>3188818534</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0.14564303</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.9072</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.7857</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="BG2" t="b">
         <v>0</v>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>HKD</t>
-        </is>
-      </c>
-      <c r="BH2" t="b">
-        <v>0</v>
+      <c r="BH2" t="n">
+        <v>7499814400</v>
       </c>
       <c r="BI2" t="n">
-        <v>10661640192</v>
+        <v>0.0107</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0.28153</v>
+        <v>391877356</v>
       </c>
       <c r="BK2" t="n">
-        <v>390949019</v>
+        <v>1635291556</v>
       </c>
       <c r="BL2" t="n">
+        <v>0.71083</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.00412</v>
+      </c>
+      <c r="BN2" t="n">
         <v>1635291556</v>
       </c>
-      <c r="BM2" t="n">
-        <v>0.71083</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0.00409</v>
-      </c>
       <c r="BO2" t="n">
-        <v>1635291556</v>
+        <v>5.973998</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.882202</v>
+        <v>0.24439245</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.33150852</v>
+        <v>1767139200</v>
       </c>
       <c r="BR2" t="n">
-        <v>1735603200</v>
+        <v>1798675200</v>
       </c>
       <c r="BS2" t="n">
         <v>1767139200</v>
       </c>
       <c r="BT2" t="n">
-        <v>1751241600</v>
+        <v>211203008</v>
       </c>
       <c r="BU2" t="n">
-        <v>-6164061184</v>
+        <v>0.15</v>
       </c>
       <c r="BV2" t="n">
-        <v>-4.37</v>
+        <v>0.87</v>
       </c>
       <c r="BW2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>2.778</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0.25384617</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>1590451200</v>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="CE2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="CG2" t="n">
+        <v>9123889152</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>5.566</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>2699531008</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>9345989632</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>1.372</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>19734337536</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>70.036</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>12.053</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>0.03167</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>0.07216</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>4272668928</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>-0.181</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.21651</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>0.13678999</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0.10361</v>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>0658.HK</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="DC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>C TRANSMISSION</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>China High Speed Transmission Equipment Group Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.16999996</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>1.41 - 1.82</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>703934</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.31000006</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.26956528</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>1.15 - 2.56</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-1.0999999</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.42968747</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>25.384617</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1756205940</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1756728000</v>
+      </c>
+      <c r="DV2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DX2" t="n">
         <v>0.87</v>
       </c>
-      <c r="BX2" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.487</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>-3.279</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>1.215909</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.27294624</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>1590451200</v>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="CF2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CH2" t="n">
-        <v>6568229888</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>4.017</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>-3251564032</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>9504487424</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>1.402</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>21894756352</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>74.012</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>13.389</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>-0.06104</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>-0.4067</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>3785765120</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>1648523648</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>1910364032</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>-0.018</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>0.17291</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>-0.14851</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>0.094069995</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>0658.HK</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="DF2" t="b">
+      <c r="DY2" t="n">
+        <v>-0.48360002</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.24881664</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.36774993</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.20120363</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>1782115692</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>finmb_34952604</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="EI2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EK2" t="b">
         <v>0</v>
       </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>1774944503</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>finmb_34952604</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DP2" t="b">
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EM2" t="b">
         <v>0</v>
       </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>C TRANSMISSION</t>
-        </is>
-      </c>
-      <c r="DR2" t="n">
-        <v>729086</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1.2941177</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>0.85 - 2.56</t>
-        </is>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.6099999</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.23828122</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>121.5909</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1756205940</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1756728000</v>
-      </c>
-      <c r="EA2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-4.37</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.04280007</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.02244131</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0.16430008</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0.092008784</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EL2" t="n">
-        <v>31.75676</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="EN2" t="b">
-        <v>0</v>
+      <c r="EN2" t="n">
+        <v>1183512600000</v>
       </c>
       <c r="EO2" t="n">
-        <v>1183512600000</v>
+        <v>-10.429445</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.47000003</v>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>1.5 - 1.97</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>China High Speed Transmission Equipment Group Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="ET2" t="inlineStr"/>
+        <v>1.46</v>
+      </c>
+      <c r="EQ2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
